--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI2"/>
+  <dimension ref="A1:AI3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -712,6 +712,124 @@
         </is>
       </c>
       <c r="AI2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>11:28:28</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="E3" t="n">
+        <v>228000</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2510</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-6.13</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.428</v>
+      </c>
+      <c r="I3" t="n">
+        <v>228000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>988</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>407</v>
+      </c>
+      <c r="R3" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>409</v>
+      </c>
+      <c r="T3" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>214</v>
+      </c>
+      <c r="V3" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="W3" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI3"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -830,6 +830,124 @@
         </is>
       </c>
       <c r="AI3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>11:32:34</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="E4" t="n">
+        <v>227900</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2459</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-8.039999999999999</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I4" t="n">
+        <v>228000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>993</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>407</v>
+      </c>
+      <c r="R4" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>414</v>
+      </c>
+      <c r="T4" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>214</v>
+      </c>
+      <c r="V4" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -948,6 +948,124 @@
         </is>
       </c>
       <c r="AI4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>11:33:57</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="E5" t="n">
+        <v>227900</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2438</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-8.83</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I5" t="n">
+        <v>228000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>993</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>407</v>
+      </c>
+      <c r="R5" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>414</v>
+      </c>
+      <c r="T5" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>214</v>
+      </c>
+      <c r="V5" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI5"/>
+  <dimension ref="A1:AI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1066,6 +1066,124 @@
         </is>
       </c>
       <c r="AI5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>11:35:18</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="E6" t="n">
+        <v>227726</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2433</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-9.01</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.442</v>
+      </c>
+      <c r="I6" t="n">
+        <v>228000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>994</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>407</v>
+      </c>
+      <c r="R6" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>414</v>
+      </c>
+      <c r="T6" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>214</v>
+      </c>
+      <c r="V6" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="W6" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI6"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1184,6 +1184,124 @@
         </is>
       </c>
       <c r="AI6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>11:36:39</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="E7" t="n">
+        <v>227650</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2430</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-9.119999999999999</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.442</v>
+      </c>
+      <c r="I7" t="n">
+        <v>228000</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>994</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>407</v>
+      </c>
+      <c r="R7" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>414</v>
+      </c>
+      <c r="T7" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U7" t="n">
+        <v>214</v>
+      </c>
+      <c r="V7" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="W7" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1302,6 +1302,124 @@
         </is>
       </c>
       <c r="AI7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>11:38:01</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="E8" t="n">
+        <v>227650</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2427</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-9.24</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.436</v>
+      </c>
+      <c r="I8" t="n">
+        <v>228000</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>994</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>408</v>
+      </c>
+      <c r="R8" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>414</v>
+      </c>
+      <c r="T8" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U8" t="n">
+        <v>215</v>
+      </c>
+      <c r="V8" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="W8" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI8"/>
+  <dimension ref="A1:AI9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1420,6 +1420,124 @@
         </is>
       </c>
       <c r="AI8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>11:40:44</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="E9" t="n">
+        <v>227900</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2399</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-10.28</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.436</v>
+      </c>
+      <c r="I9" t="n">
+        <v>228000</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>994</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>408</v>
+      </c>
+      <c r="R9" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>414</v>
+      </c>
+      <c r="T9" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U9" t="n">
+        <v>215</v>
+      </c>
+      <c r="V9" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI9"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1538,6 +1538,124 @@
         </is>
       </c>
       <c r="AI9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>11:42:03</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="E10" t="n">
+        <v>227810</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2392</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-10.55</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.436</v>
+      </c>
+      <c r="I10" t="n">
+        <v>228000</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>994</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>408</v>
+      </c>
+      <c r="R10" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>414</v>
+      </c>
+      <c r="T10" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U10" t="n">
+        <v>215</v>
+      </c>
+      <c r="V10" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI10"/>
+  <dimension ref="A1:AI11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1658,6 +1658,124 @@
       <c r="AI10" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>11:43:29</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="E11" t="n">
+        <v>228150</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2391</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-10.58</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.441</v>
+      </c>
+      <c r="I11" t="n">
+        <v>228000</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>996</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>408</v>
+      </c>
+      <c r="R11" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>416</v>
+      </c>
+      <c r="T11" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U11" t="n">
+        <v>215</v>
+      </c>
+      <c r="V11" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>4/4</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI11"/>
+  <dimension ref="A1:AI12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1776,6 +1776,118 @@
       <c r="AI11" t="inlineStr">
         <is>
           <t>4/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>18:31:19</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="E12" t="n">
+        <v>228805</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2249</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-15.89</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.441</v>
+      </c>
+      <c r="I12" t="n">
+        <v>229000</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>1140</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>467</v>
+      </c>
+      <c r="R12" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>475</v>
+      </c>
+      <c r="T12" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U12" t="n">
+        <v>240</v>
+      </c>
+      <c r="V12" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI12"/>
+  <dimension ref="A1:AI13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1888,6 +1888,124 @@
       <c r="AI12" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>18:32:25</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="E13" t="n">
+        <v>229000</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2249</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-15.89</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.441</v>
+      </c>
+      <c r="I13" t="n">
+        <v>229000</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>1140</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>467</v>
+      </c>
+      <c r="R13" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>475</v>
+      </c>
+      <c r="T13" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U13" t="n">
+        <v>240</v>
+      </c>
+      <c r="V13" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>4/4</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI13"/>
+  <dimension ref="A1:AI14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2004,6 +2004,124 @@
         </is>
       </c>
       <c r="AI13" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>18:33:31</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="E14" t="n">
+        <v>229000</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2249</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-15.89</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.441</v>
+      </c>
+      <c r="I14" t="n">
+        <v>229000</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>1140</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>467</v>
+      </c>
+      <c r="R14" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>475</v>
+      </c>
+      <c r="T14" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U14" t="n">
+        <v>240</v>
+      </c>
+      <c r="V14" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
         <is>
           <t>4/4</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI14"/>
+  <dimension ref="A1:AI15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2122,6 +2122,124 @@
         </is>
       </c>
       <c r="AI14" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>18:34:35</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="E15" t="n">
+        <v>229153</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2246</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-16.01</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="I15" t="n">
+        <v>229000</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>1140</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>457</v>
+      </c>
+      <c r="R15" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>475</v>
+      </c>
+      <c r="T15" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U15" t="n">
+        <v>239</v>
+      </c>
+      <c r="V15" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="W15" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
         <is>
           <t>4/4</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI15"/>
+  <dimension ref="A1:AI16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2240,6 +2240,124 @@
         </is>
       </c>
       <c r="AI15" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>18:35:42</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="E16" t="n">
+        <v>229153</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2246</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-16.01</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.503</v>
+      </c>
+      <c r="I16" t="n">
+        <v>229000</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>1144</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>457</v>
+      </c>
+      <c r="R16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>475</v>
+      </c>
+      <c r="T16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U16" t="n">
+        <v>239</v>
+      </c>
+      <c r="V16" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="W16" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
         <is>
           <t>4/4</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI16"/>
+  <dimension ref="A1:AI17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2358,6 +2358,124 @@
         </is>
       </c>
       <c r="AI16" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>18:36:50</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="E17" t="n">
+        <v>229153</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2245</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-16.04</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.498</v>
+      </c>
+      <c r="I17" t="n">
+        <v>229000</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>1144</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>458</v>
+      </c>
+      <c r="R17" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>475</v>
+      </c>
+      <c r="T17" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U17" t="n">
+        <v>240</v>
+      </c>
+      <c r="V17" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="W17" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
         <is>
           <t>4/4</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI17"/>
+  <dimension ref="A1:AI18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2476,6 +2476,124 @@
         </is>
       </c>
       <c r="AI17" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>18:37:58</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="E18" t="n">
+        <v>229153</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2245</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-16.04</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.493</v>
+      </c>
+      <c r="I18" t="n">
+        <v>229000</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>1142</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>458</v>
+      </c>
+      <c r="R18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S18" t="n">
+        <v>473</v>
+      </c>
+      <c r="T18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U18" t="n">
+        <v>240</v>
+      </c>
+      <c r="V18" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="W18" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
         <is>
           <t>4/4</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI18"/>
+  <dimension ref="A1:AI19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2594,6 +2594,124 @@
         </is>
       </c>
       <c r="AI18" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>18:39:06</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="E19" t="n">
+        <v>229300</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2244</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-16.08</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.551</v>
+      </c>
+      <c r="I19" t="n">
+        <v>229000</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>1143</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>448</v>
+      </c>
+      <c r="R19" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S19" t="n">
+        <v>475</v>
+      </c>
+      <c r="T19" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U19" t="n">
+        <v>240</v>
+      </c>
+      <c r="V19" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="W19" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
         <is>
           <t>4/4</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI19"/>
+  <dimension ref="A1:AI20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2712,6 +2712,124 @@
         </is>
       </c>
       <c r="AI19" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>18:40:15</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="E20" t="n">
+        <v>229415</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2242</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-16.16</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.543</v>
+      </c>
+      <c r="I20" t="n">
+        <v>229000</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>1142</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>449</v>
+      </c>
+      <c r="R20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S20" t="n">
+        <v>474</v>
+      </c>
+      <c r="T20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U20" t="n">
+        <v>240</v>
+      </c>
+      <c r="V20" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="W20" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
         <is>
           <t>4/4</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI20"/>
+  <dimension ref="A1:AI21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2830,6 +2830,124 @@
         </is>
       </c>
       <c r="AI20" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>18:41:22</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E21" t="n">
+        <v>229425</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2241</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-16.19</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.555</v>
+      </c>
+      <c r="I21" t="n">
+        <v>229000</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>1147</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>449</v>
+      </c>
+      <c r="R21" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S21" t="n">
+        <v>478</v>
+      </c>
+      <c r="T21" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U21" t="n">
+        <v>240</v>
+      </c>
+      <c r="V21" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="W21" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
         <is>
           <t>4/4</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI21"/>
+  <dimension ref="A1:AI22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2948,6 +2948,124 @@
         </is>
       </c>
       <c r="AI21" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>18:42:30</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="E22" t="n">
+        <v>229415</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2240</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-16.23</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.542</v>
+      </c>
+      <c r="I22" t="n">
+        <v>229000</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>1149</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>452</v>
+      </c>
+      <c r="R22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S22" t="n">
+        <v>481</v>
+      </c>
+      <c r="T22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U22" t="n">
+        <v>242</v>
+      </c>
+      <c r="V22" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="W22" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
         <is>
           <t>4/4</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI22"/>
+  <dimension ref="A1:AI23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3068,6 +3068,124 @@
       <c r="AI22" t="inlineStr">
         <is>
           <t>4/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>18:43:38</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="E23" t="n">
+        <v>229415</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2240</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-16.23</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.536</v>
+      </c>
+      <c r="I23" t="n">
+        <v>229000</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>1149</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>453</v>
+      </c>
+      <c r="R23" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S23" t="n">
+        <v>481</v>
+      </c>
+      <c r="T23" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U23" t="n">
+        <v>242</v>
+      </c>
+      <c r="V23" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="W23" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>3/3</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI23"/>
+  <dimension ref="A1:AI24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3184,6 +3184,124 @@
         </is>
       </c>
       <c r="AI23" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>18:44:46</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="E24" t="n">
+        <v>229415</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2240</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-16.23</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.544</v>
+      </c>
+      <c r="I24" t="n">
+        <v>229000</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>1150</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>452</v>
+      </c>
+      <c r="R24" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S24" t="n">
+        <v>480</v>
+      </c>
+      <c r="T24" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U24" t="n">
+        <v>241</v>
+      </c>
+      <c r="V24" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="W24" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
         <is>
           <t>3/3</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI24"/>
+  <dimension ref="A1:AI25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3304,6 +3304,118 @@
       <c r="AI24" t="inlineStr">
         <is>
           <t>3/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>18:46:42</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E25" t="n">
+        <v>229200</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2238</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-16.31</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I25" t="n">
+        <v>229000</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>1148</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>452</v>
+      </c>
+      <c r="R25" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S25" t="n">
+        <v>480</v>
+      </c>
+      <c r="T25" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U25" t="n">
+        <v>241</v>
+      </c>
+      <c r="V25" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="W25" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI25"/>
+  <dimension ref="A1:AI26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3414,6 +3414,124 @@
         </is>
       </c>
       <c r="AI25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>18:47:49</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E26" t="n">
+        <v>229200</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2238</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-16.31</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I26" t="n">
+        <v>229000</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>1148</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>452</v>
+      </c>
+      <c r="R26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S26" t="n">
+        <v>480</v>
+      </c>
+      <c r="T26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U26" t="n">
+        <v>241</v>
+      </c>
+      <c r="V26" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="W26" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI26"/>
+  <dimension ref="A1:AI27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3532,6 +3532,124 @@
         </is>
       </c>
       <c r="AI26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>18:48:55</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="E27" t="n">
+        <v>229230</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2237</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-16.34</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.507</v>
+      </c>
+      <c r="I27" t="n">
+        <v>229000</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>1148</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>458</v>
+      </c>
+      <c r="R27" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S27" t="n">
+        <v>480</v>
+      </c>
+      <c r="T27" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U27" t="n">
+        <v>241</v>
+      </c>
+      <c r="V27" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="W27" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI27"/>
+  <dimension ref="A1:AI28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3650,6 +3650,124 @@
         </is>
       </c>
       <c r="AI27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>18:50:02</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="E28" t="n">
+        <v>229230</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2237</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-16.34</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2.507</v>
+      </c>
+      <c r="I28" t="n">
+        <v>229000</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>1148</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>458</v>
+      </c>
+      <c r="R28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S28" t="n">
+        <v>480</v>
+      </c>
+      <c r="T28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U28" t="n">
+        <v>241</v>
+      </c>
+      <c r="V28" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="W28" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI28"/>
+  <dimension ref="A1:AI29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3768,6 +3768,124 @@
         </is>
       </c>
       <c r="AI28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>18:51:08</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="E29" t="n">
+        <v>229230</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2237</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-16.34</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I29" t="n">
+        <v>229000</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>1149</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>456</v>
+      </c>
+      <c r="R29" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S29" t="n">
+        <v>481</v>
+      </c>
+      <c r="T29" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U29" t="n">
+        <v>240</v>
+      </c>
+      <c r="V29" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="W29" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI29"/>
+  <dimension ref="A1:AI30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3886,6 +3886,124 @@
         </is>
       </c>
       <c r="AI29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>18:52:15</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="E30" t="n">
+        <v>229230</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2237</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-16.34</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.514</v>
+      </c>
+      <c r="I30" t="n">
+        <v>229000</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>1149</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>457</v>
+      </c>
+      <c r="R30" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S30" t="n">
+        <v>481</v>
+      </c>
+      <c r="T30" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U30" t="n">
+        <v>240</v>
+      </c>
+      <c r="V30" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="W30" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI30"/>
+  <dimension ref="A1:AI31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4004,6 +4004,118 @@
         </is>
       </c>
       <c r="AI30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>18:54:42</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="E31" t="n">
+        <v>229221</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2235</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-16.42</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.521</v>
+      </c>
+      <c r="I31" t="n">
+        <v>229000</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>1152</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>457</v>
+      </c>
+      <c r="R31" t="n">
+        <v>230000</v>
+      </c>
+      <c r="S31" t="n">
+        <v>483</v>
+      </c>
+      <c r="T31" t="n">
+        <v>230000</v>
+      </c>
+      <c r="U31" t="n">
+        <v>240</v>
+      </c>
+      <c r="V31" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="W31" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI31"/>
+  <dimension ref="A1:AI32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4116,6 +4116,124 @@
         </is>
       </c>
       <c r="AI31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>18:55:50</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E32" t="n">
+        <v>229510</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2233</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-16.49</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.761</v>
+      </c>
+      <c r="I32" t="n">
+        <v>230000</v>
+      </c>
+      <c r="J32" t="n">
+        <v>482</v>
+      </c>
+      <c r="K32" t="n">
+        <v>481</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>240</v>
+      </c>
+      <c r="N32" t="n">
+        <v>239</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>1679</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2206</v>
+      </c>
+      <c r="R32" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S32" t="n">
+        <v>528</v>
+      </c>
+      <c r="T32" t="n">
+        <v>240000</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1749</v>
+      </c>
+      <c r="V32" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="W32" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>-4.37</v>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI32"/>
+  <dimension ref="A1:AI33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4234,6 +4234,124 @@
         </is>
       </c>
       <c r="AI32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>18:56:57</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E33" t="n">
+        <v>229510</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2233</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-16.49</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.761</v>
+      </c>
+      <c r="I33" t="n">
+        <v>230000</v>
+      </c>
+      <c r="J33" t="n">
+        <v>482</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>240</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>1679</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2206</v>
+      </c>
+      <c r="R33" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S33" t="n">
+        <v>528</v>
+      </c>
+      <c r="T33" t="n">
+        <v>240000</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1749</v>
+      </c>
+      <c r="V33" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="W33" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>-4.37</v>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI33"/>
+  <dimension ref="A1:AI34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4352,6 +4352,124 @@
         </is>
       </c>
       <c r="AI33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>18:58:03</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E34" t="n">
+        <v>229510</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2233</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-16.49</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="I34" t="n">
+        <v>230000</v>
+      </c>
+      <c r="J34" t="n">
+        <v>482</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>240</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>1677</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2206</v>
+      </c>
+      <c r="R34" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S34" t="n">
+        <v>528</v>
+      </c>
+      <c r="T34" t="n">
+        <v>240000</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1749</v>
+      </c>
+      <c r="V34" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="W34" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>-4.37</v>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI34"/>
+  <dimension ref="A1:AI35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4470,6 +4470,124 @@
         </is>
       </c>
       <c r="AI34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>18:59:10</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E35" t="n">
+        <v>229510</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2233</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-16.49</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="I35" t="n">
+        <v>230000</v>
+      </c>
+      <c r="J35" t="n">
+        <v>482</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>240</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>1677</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2207</v>
+      </c>
+      <c r="R35" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S35" t="n">
+        <v>528</v>
+      </c>
+      <c r="T35" t="n">
+        <v>240000</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1750</v>
+      </c>
+      <c r="V35" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="W35" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>-4.37</v>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI35"/>
+  <dimension ref="A1:AI36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4590,6 +4590,124 @@
       <c r="AI35" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>19:02:29</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E36" t="n">
+        <v>230400</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2221</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-16.94</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="I36" t="n">
+        <v>230000</v>
+      </c>
+      <c r="J36" t="n">
+        <v>481</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>234</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-6</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>1679</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2199</v>
+      </c>
+      <c r="R36" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S36" t="n">
+        <v>530</v>
+      </c>
+      <c r="T36" t="n">
+        <v>240000</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1748</v>
+      </c>
+      <c r="V36" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="W36" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI36"/>
+  <dimension ref="A1:AI37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4706,6 +4706,124 @@
         </is>
       </c>
       <c r="AI36" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>19:03:36</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="E37" t="n">
+        <v>230800</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2221</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-16.94</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="I37" t="n">
+        <v>231000</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-481</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-234</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>1323</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2157</v>
+      </c>
+      <c r="R37" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S37" t="n">
+        <v>530</v>
+      </c>
+      <c r="T37" t="n">
+        <v>240000</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1748</v>
+      </c>
+      <c r="V37" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="W37" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>-3.83</v>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
         <is>
           <t>0/4</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI37"/>
+  <dimension ref="A1:AI38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4826,6 +4826,124 @@
       <c r="AI37" t="inlineStr">
         <is>
           <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>19:04:42</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E38" t="n">
+        <v>230447</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2218</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-17.05</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="I38" t="n">
+        <v>230000</v>
+      </c>
+      <c r="J38" t="n">
+        <v>481</v>
+      </c>
+      <c r="K38" t="n">
+        <v>481</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>234</v>
+      </c>
+      <c r="N38" t="n">
+        <v>234</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>1675</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2188</v>
+      </c>
+      <c r="R38" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S38" t="n">
+        <v>527</v>
+      </c>
+      <c r="T38" t="n">
+        <v>240000</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1737</v>
+      </c>
+      <c r="V38" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="W38" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>-3.98</v>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>0/3</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI38"/>
+  <dimension ref="A1:AI39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4942,6 +4942,124 @@
         </is>
       </c>
       <c r="AI38" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>19:05:51</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E39" t="n">
+        <v>230447</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2218</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-17.05</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="I39" t="n">
+        <v>230000</v>
+      </c>
+      <c r="J39" t="n">
+        <v>482</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>234</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>1675</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2189</v>
+      </c>
+      <c r="R39" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S39" t="n">
+        <v>526</v>
+      </c>
+      <c r="T39" t="n">
+        <v>240000</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1737</v>
+      </c>
+      <c r="V39" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="W39" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>-3.98</v>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
         <is>
           <t>0/3</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI39"/>
+  <dimension ref="A1:AI40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5060,6 +5060,124 @@
         </is>
       </c>
       <c r="AI39" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>19:06:57</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E40" t="n">
+        <v>230447</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2218</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-17.05</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="I40" t="n">
+        <v>230000</v>
+      </c>
+      <c r="J40" t="n">
+        <v>482</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>233</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>1677</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2192</v>
+      </c>
+      <c r="R40" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S40" t="n">
+        <v>526</v>
+      </c>
+      <c r="T40" t="n">
+        <v>240000</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1741</v>
+      </c>
+      <c r="V40" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="W40" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>-3.98</v>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
         <is>
           <t>0/3</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI40"/>
+  <dimension ref="A1:AI41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5178,6 +5178,124 @@
         </is>
       </c>
       <c r="AI40" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>19:08:05</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E41" t="n">
+        <v>230567</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2218</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-17.05</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="I41" t="n">
+        <v>231000</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-482</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-233</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>1321</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2148</v>
+      </c>
+      <c r="R41" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S41" t="n">
+        <v>526</v>
+      </c>
+      <c r="T41" t="n">
+        <v>240000</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1740</v>
+      </c>
+      <c r="V41" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="W41" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>-3.93</v>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
         <is>
           <t>0/3</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI41"/>
+  <dimension ref="A1:AI42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5296,6 +5296,124 @@
         </is>
       </c>
       <c r="AI41" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>19:09:11</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E42" t="n">
+        <v>230290</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2216</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-17.13</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="I42" t="n">
+        <v>230000</v>
+      </c>
+      <c r="J42" t="n">
+        <v>479</v>
+      </c>
+      <c r="K42" t="n">
+        <v>479</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>233</v>
+      </c>
+      <c r="N42" t="n">
+        <v>233</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>1672</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2191</v>
+      </c>
+      <c r="R42" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S42" t="n">
+        <v>525</v>
+      </c>
+      <c r="T42" t="n">
+        <v>240000</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1740</v>
+      </c>
+      <c r="V42" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="W42" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>-4.05</v>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
         <is>
           <t>0/3</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI42"/>
+  <dimension ref="A1:AI43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5414,6 +5414,124 @@
         </is>
       </c>
       <c r="AI42" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>19:10:18</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E43" t="n">
+        <v>230290</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2216</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-17.13</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="I43" t="n">
+        <v>230000</v>
+      </c>
+      <c r="J43" t="n">
+        <v>478</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>232</v>
+      </c>
+      <c r="N43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>1670</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2189</v>
+      </c>
+      <c r="R43" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S43" t="n">
+        <v>525</v>
+      </c>
+      <c r="T43" t="n">
+        <v>240000</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1739</v>
+      </c>
+      <c r="V43" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="W43" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>-4.05</v>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
         <is>
           <t>0/3</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI43"/>
+  <dimension ref="A1:AI44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5532,6 +5532,124 @@
         </is>
       </c>
       <c r="AI43" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>19:11:26</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E44" t="n">
+        <v>230290</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2216</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-17.13</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="I44" t="n">
+        <v>230000</v>
+      </c>
+      <c r="J44" t="n">
+        <v>478</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>234</v>
+      </c>
+      <c r="N44" t="n">
+        <v>2</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>1670</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2192</v>
+      </c>
+      <c r="R44" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S44" t="n">
+        <v>525</v>
+      </c>
+      <c r="T44" t="n">
+        <v>240000</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1740</v>
+      </c>
+      <c r="V44" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="W44" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>-4.05</v>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
         <is>
           <t>0/3</t>
         </is>

--- a/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
+++ b/backend/signal_logs/2026-09-02/index_tracker_SILVER_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI44"/>
+  <dimension ref="A1:AI46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5650,6 +5650,242 @@
         </is>
       </c>
       <c r="AI44" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>19:12:34</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E45" t="n">
+        <v>230290</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2216</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-17.13</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="I45" t="n">
+        <v>230000</v>
+      </c>
+      <c r="J45" t="n">
+        <v>479</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>234</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>1670</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2192</v>
+      </c>
+      <c r="R45" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S45" t="n">
+        <v>525</v>
+      </c>
+      <c r="T45" t="n">
+        <v>240000</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1740</v>
+      </c>
+      <c r="V45" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="W45" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>-4.05</v>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>19:14:01</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E46" t="n">
+        <v>230900</v>
+      </c>
+      <c r="F46" t="n">
+        <v>2216</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-17.13</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="I46" t="n">
+        <v>231000</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-479</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>-234</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>1317</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>2148</v>
+      </c>
+      <c r="R46" t="n">
+        <v>240000</v>
+      </c>
+      <c r="S46" t="n">
+        <v>525</v>
+      </c>
+      <c r="T46" t="n">
+        <v>240000</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1740</v>
+      </c>
+      <c r="V46" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="W46" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>240000</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>-3.79</v>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>⚠ Neutral but rising</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
         <is>
           <t>0/3</t>
         </is>
